--- a/output/Data and Chart Outputs/china_nea_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nea_capacity_monthly.xlsx
@@ -157,7 +157,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China installed capacity by type (NEA) (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China installed capacity by type (NEA) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -187,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$61</f>
+              <f>'Chart'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -215,12 +216,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$61</f>
+              <f>'Chart'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$61</f>
+              <f>'Chart'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -271,12 +272,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$61</f>
+              <f>'Chart'!$E$2:$E$62</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$61</f>
+              <f>'Chart'!$F$2:$F$62</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +328,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$61</f>
+              <f>'Chart'!$G$2:$G$62</f>
             </numRef>
           </val>
         </ser>
@@ -811,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2231,6 +2232,29 @@
         <v>1288.04</v>
       </c>
       <c r="G61" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B62" t="n">
+        <v>457.25</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1593.43</v>
+      </c>
+      <c r="D62" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="E62" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1312.87</v>
+      </c>
+      <c r="G62" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -2246,7 +2270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5744,6 +5768,65 @@
       <c r="Q61" t="inlineStr">
         <is>
           <t>https://www.nea.gov.cn/20260825/1430d07985474c5b8110552785f1c74b/c.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4132.14</v>
+      </c>
+      <c r="C62" t="n">
+        <v>457.25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1593.43</v>
+      </c>
+      <c r="E62" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="F62" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1312.87</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I62" t="n">
+        <v>252.93</v>
+      </c>
+      <c r="J62" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="K62" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="L62" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M62" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="N62" t="n">
+        <v>110.83</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>OCR of image table</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://www.nea.gov.cn/20261026/7e48f52542c94c0f99c166262453627d/c.html</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7708,6 +7791,38 @@
         </is>
       </c>
       <c r="F61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>国家能源局发布2026年1-9月份全国电力统计数据</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.nea.gov.cn/20261026/7e48f52542c94c0f99c166262453627d/c.html</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OCR of image table</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
